--- a/changes/9mm-mags.xlsx
+++ b/changes/9mm-mags.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B998C7C-F947-4F63-99C3-A4457FCB8435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2BA538-C904-47E1-9AAC-8F865DC057B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="97">
   <si>
     <t>new</t>
   </si>
@@ -59,7 +59,7 @@
     <t>magazine_capacity</t>
   </si>
   <si>
-    <t>bullet_deviation</t>
+    <t>barrel_deviation</t>
   </si>
   <si>
     <t>bullet_damage</t>
@@ -68,7 +68,7 @@
     <t>bullet_velocity</t>
   </si>
   <si>
-    <t>buck_bullet_deviation</t>
+    <t>buck_barrel_deviation</t>
   </si>
   <si>
     <t>fire_rate</t>
@@ -89,211 +89,241 @@
     <t>formula</t>
   </si>
   <si>
+    <t>kosch_9x19_31r_stick_magazine</t>
+  </si>
+  <si>
+    <t>KOSCH 9x19 31R Stick</t>
+  </si>
+  <si>
+    <t>kosch_9x19_17r_magazine</t>
+  </si>
+  <si>
+    <t>KOSCH 9x19 17R</t>
+  </si>
+  <si>
+    <t>fst_kosch_9x19_50r_drum_magazine</t>
+  </si>
+  <si>
+    <t>SGM Tactical PF940 17 50R 9x19 Drum</t>
+  </si>
+  <si>
+    <t>kosch_default_9x19_mag_plate</t>
+  </si>
+  <si>
+    <t>KOSCH Default 9x19 Magazine Plate</t>
+  </si>
+  <si>
+    <t>9x19_pf940_std_17r_vector</t>
+  </si>
+  <si>
+    <t>PF940 9x19 17R</t>
+  </si>
+  <si>
+    <t>9x19_sgmt_drum50r_vector</t>
+  </si>
+  <si>
+    <t>SGMT 9x19 50R Drum</t>
+  </si>
+  <si>
+    <t>vector_17r_plate</t>
+  </si>
+  <si>
+    <t>Magazine</t>
+  </si>
+  <si>
+    <t>9x19_kriss_magex2_vector</t>
+  </si>
+  <si>
+    <t>9x19 KALIS MagEx2 For PF940 (+23 Rounds)</t>
+  </si>
+  <si>
+    <t>9x19_glock_stick_31r</t>
+  </si>
+  <si>
     <t>Glock 9x19 31R Stick</t>
   </si>
   <si>
-    <t>9x19_glock_stick_31r</t>
-  </si>
-  <si>
-    <t>SGMT 9x19 50R Drum</t>
+    <t>pf940_gen5_9x19_17r_magazine</t>
+  </si>
+  <si>
+    <t>PF940 17 Gen5 17R 9x19</t>
   </si>
   <si>
     <t>9x19_sgmt_50r_drum</t>
   </si>
   <si>
-    <t>wilson_combat_edc_x9_18r_magazine</t>
-  </si>
-  <si>
-    <t>EDC X9 Std. 18r</t>
-  </si>
-  <si>
-    <t>wilson_combat_edc_x9_15r_magazine</t>
-  </si>
-  <si>
-    <t>EDC X9 Std. 15r</t>
-  </si>
-  <si>
-    <t>wilson_combat_edc_x9_10r_magazine</t>
-  </si>
-  <si>
-    <t>EDC X9 Std. 10r</t>
+    <t>9x19_glock_stick_31r_vector</t>
+  </si>
+  <si>
+    <t>PF940 9x19 31R Stick</t>
+  </si>
+  <si>
+    <t>9x19_kriss_magex2_glock</t>
+  </si>
+  <si>
+    <t>9x19 KRISS MagEx2 For Glock (+23 Rounds)</t>
+  </si>
+  <si>
+    <t>whitner_defense_edc_x9_mag_bottomplate</t>
+  </si>
+  <si>
+    <t>Whitner Defense EDC X9 Magazine</t>
+  </si>
+  <si>
+    <t>whitner_defense_edc_x9_18r_magazine</t>
+  </si>
+  <si>
+    <t>Whitner Defense EDC X9 Std. 18r</t>
+  </si>
+  <si>
+    <t>whitner_defense_edc_x9_15r_magazine</t>
+  </si>
+  <si>
+    <t>Whitner Defense EDC X9 Std. 15r</t>
+  </si>
+  <si>
+    <t>whitner_defense_edc_x9_10r_magazine</t>
+  </si>
+  <si>
+    <t>Whitner Defense EDC X9 Std. 10r</t>
+  </si>
+  <si>
+    <t>sig_sauer_p320_mag_bottom_plate</t>
+  </si>
+  <si>
+    <t>Sic Stürmer P320 Mag</t>
+  </si>
+  <si>
+    <t>sig_sauer_p320_9x19_17r_mag</t>
+  </si>
+  <si>
+    <t>Sic Stürmer P320 9x19 17R</t>
+  </si>
+  <si>
+    <t>sig_sauer_p320_9x19_21r_mag</t>
+  </si>
+  <si>
+    <t>Sic Stürmer P320 9x19 21R</t>
+  </si>
+  <si>
+    <t>sig_sauer_p320_9x19_30r_mag</t>
+  </si>
+  <si>
+    <t>Sic Stürmer P320 9x19 30R</t>
   </si>
   <si>
     <t>hk_ump9_9x19_30r_mag</t>
   </si>
   <si>
-    <t>HK UMP9 9x19 30R</t>
-  </si>
-  <si>
-    <t>sig_sauer_p320_mag_bottom_plate</t>
-  </si>
-  <si>
-    <t>Sig Sauer P320 Mag Bottom Plate</t>
-  </si>
-  <si>
-    <t>sig_sauer_p320_9x19_17r_mag</t>
-  </si>
-  <si>
-    <t>Sig Sauer P320 9x19 17r Mag</t>
-  </si>
-  <si>
-    <t>sig_sauer_p320_9x19_21r_mag</t>
-  </si>
-  <si>
-    <t>Sig Sauer P320 9x19 21r Mag</t>
-  </si>
-  <si>
-    <t>sig_sauer_p320_9x19_30r_mag</t>
-  </si>
-  <si>
-    <t>Sig Sauer P320 9x19 30r Mag</t>
-  </si>
-  <si>
-    <t>wilson_combat_edc_x9_mag_bottomplate</t>
-  </si>
-  <si>
-    <t>Wilson Combat EDC X9 Magazine</t>
-  </si>
-  <si>
-    <t>glock17_17r_magazine_bottom_plate</t>
-  </si>
-  <si>
-    <t>9x19_kriss_magex2_glock</t>
-  </si>
-  <si>
-    <t>9x19 KRISS MagEx2 For Glock (+23 Rounds)</t>
-  </si>
-  <si>
-    <t>izhmash_pp-19-01_vityaz_9x19_30r_mag</t>
-  </si>
-  <si>
-    <t>Izhmash PP-19-01 Vityaz 9x19 30R</t>
-  </si>
-  <si>
-    <t>izhmash_saiga_9_9x19_pinned_10r_mag</t>
-  </si>
-  <si>
-    <t>Izhmash Saiga-9 9x19 Pinned 10R</t>
+    <t>UMC-9 9x19 30R</t>
+  </si>
+  <si>
+    <t>kazarov_pp-19-01_mag_bottom_plate</t>
+  </si>
+  <si>
+    <t>Kazarov PP-19-01</t>
+  </si>
+  <si>
+    <t>kazarov_pp-19-01_vityaz_9x19_30r_mag</t>
+  </si>
+  <si>
+    <t>Kazarov PP-19-01 Vityaz 9x19 30R</t>
+  </si>
+  <si>
+    <t>kazarov_saiga_9_9x19_pinned_10r_mag</t>
+  </si>
+  <si>
+    <t>Kazarov Saiga-9 9x19 Pinned 10R</t>
   </si>
   <si>
     <t>kalashnikov_usa_kp9_9x19_50r_drum_mag</t>
   </si>
   <si>
-    <t>Kalashnikov USA KP9 9x19 50R Drum Mag</t>
-  </si>
-  <si>
-    <t>izhmash_pp-19-01_mag_bottom_plate</t>
-  </si>
-  <si>
-    <t>Izhmash PP-19-01 Bottom Plate</t>
+    <t>Kazarov USA KP9 9x19 50R Drum</t>
+  </si>
+  <si>
+    <t>hk_mp5_std_mag_plate</t>
+  </si>
+  <si>
+    <t>MPi-54 Std. Curved Mag</t>
   </si>
   <si>
     <t>hk_mp5_std_curved_30r_9x19_magazine</t>
   </si>
   <si>
-    <t>HK MP5 Std. Curved 30rd 9x19 Magazine</t>
+    <t>MPi-54 Std. Curved 9x19 30R Mag</t>
   </si>
   <si>
     <t>hk_mp5_straight_30r_9x19_magazine</t>
   </si>
   <si>
-    <t>HK MP5 Straight 30rd 9x19 Magazine</t>
-  </si>
-  <si>
-    <t>x_products_mp5_50r_9x19_drum</t>
-  </si>
-  <si>
-    <t>X Products MP5 50rd 9x19 Drum</t>
-  </si>
-  <si>
-    <t>hk_mp5_std_mag_plate</t>
-  </si>
-  <si>
-    <t>HK MP5 Std. Magazine Plate</t>
+    <t>MPi-54 Straight 9x19 30R Mag</t>
+  </si>
+  <si>
+    <t>cartesia_productions_mp5_50r_9x19_drum</t>
+  </si>
+  <si>
+    <t>Cartesia Productions MPi-54 9x19 50R Drum</t>
   </si>
   <si>
     <t>steyr_aug_para_mp88_9x19_25r_mag</t>
   </si>
   <si>
-    <t>Steyr AUG MP88 9x19 25R</t>
+    <t>Löwenherz AUG MP88 9x19 25R</t>
   </si>
   <si>
     <t>steyr_mpi_69_81_9x19_32r_mag</t>
   </si>
   <si>
-    <t>Steyr MPI69/81 9x19 32R</t>
+    <t>Löwenherz MPi 69/81 9x19 32R</t>
   </si>
   <si>
     <t>roch_custom_steyr_aug_9x19_40r_mag</t>
   </si>
   <si>
-    <t>Roch Custom Steyr AUG Para 9x19 40R</t>
-  </si>
-  <si>
-    <t>colt_32rd</t>
-  </si>
-  <si>
-    <t>Colt 9x19 32rnd</t>
-  </si>
-  <si>
-    <t>duramag_colt_ar9_20r_mag</t>
-  </si>
-  <si>
-    <t>Duramag Colt AR-9 20Rnd</t>
-  </si>
-  <si>
-    <t>duramag_colt_ar9_10r_mag</t>
-  </si>
-  <si>
-    <t>Duramag Colt AR-9 10Rnd</t>
-  </si>
-  <si>
-    <t>custom_colt_smg_9x19_50r_mag</t>
-  </si>
-  <si>
-    <t>Custom Colt SMG 9x19 50rnd Magazine</t>
-  </si>
-  <si>
-    <t>taylor_freelance_colt_smg_10r_mag_extension</t>
-  </si>
-  <si>
-    <t>Taylor Freelance Colt SMG 10r Mag Extension</t>
-  </si>
-  <si>
-    <t>custom_colt_smg_9x19_50r_extension</t>
-  </si>
-  <si>
-    <t>Custom Colt SMG 50rnd Magazine Extension</t>
-  </si>
-  <si>
-    <t>custom_colt_smg_mag_coupler</t>
-  </si>
-  <si>
-    <t>Custom Colt SMG Mag Coupler</t>
-  </si>
-  <si>
-    <t>Glock 17R Magazine Bottom Plate</t>
-  </si>
-  <si>
-    <t>pf940_9x19_stick_31r_magazine</t>
-  </si>
-  <si>
-    <t>pf940_gen5_9x19_17r_magazine</t>
-  </si>
-  <si>
-    <t>sgm_tactical_pf940_9x19_50r_drum_magazine</t>
-  </si>
-  <si>
-    <t>9x19_kriss_magex2_vector</t>
-  </si>
-  <si>
-    <t>PF940 9x19 31R Stick</t>
-  </si>
-  <si>
-    <t>PF940 9x19 17R</t>
-  </si>
-  <si>
-    <t>9x19 KRISS MagEx2 For PF940 (+23 Rounds)</t>
+    <t>Roch Custom Löwenherz AUG Para 9x19 40R</t>
+  </si>
+  <si>
+    <t>hart_32rd</t>
+  </si>
+  <si>
+    <t>Hart 9x19 32rnd</t>
+  </si>
+  <si>
+    <t>evermag_hart_ar9_20r_mag</t>
+  </si>
+  <si>
+    <t>EVERMAG Hart AR-9 20Rnd</t>
+  </si>
+  <si>
+    <t>evermag_hart_ar9_10r_mag</t>
+  </si>
+  <si>
+    <t>EVERMAG Hart AR-9 10Rnd</t>
+  </si>
+  <si>
+    <t>custom_hart_smg_9x19_50r_mag</t>
+  </si>
+  <si>
+    <t>Custom Hart SMG 9x19 50rnd Magazine</t>
+  </si>
+  <si>
+    <t>tyler_freelance_hart_smg_10r_mag_extension</t>
+  </si>
+  <si>
+    <t>Tyler Freelance Hart SMG 10R Mag Extension</t>
+  </si>
+  <si>
+    <t>custom_hart_smg_9x19_50r_extension</t>
+  </si>
+  <si>
+    <t>Custom Hart SMG 9x19 50R Extension</t>
+  </si>
+  <si>
+    <t>custom_hart_smg_mag_coupler</t>
+  </si>
+  <si>
+    <t>Custom Hart SMG 9x19</t>
   </si>
 </sst>
 </file>
@@ -305,7 +335,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -321,13 +350,11 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -350,12 +377,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,11 +448,11 @@
         <a:srgbClr val="0563C1"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -426,7 +460,7 @@
         <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Sheets">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -435,23 +469,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -461,23 +495,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -485,26 +519,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -539,17 +570,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -572,11 +603,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T998"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" customWidth="1"/>
-    <col min="2" max="2" width="44.140625" customWidth="1"/>
-    <col min="3" max="20" width="6.7109375" customWidth="1"/>
+    <col min="1" max="1" width="46" style="2" customWidth="1"/>
+    <col min="2" max="2" width="48" style="2" customWidth="1"/>
+    <col min="3" max="18" width="8.7109375" style="2" customWidth="1"/>
+    <col min="19" max="20" width="6.7109375" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="14.42578125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -603,792 +636,837 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="2">
-        <v>-3</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.35</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2">
-        <v>31</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2">
+    <row r="3" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4">
+        <v>17</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="4">
         <v>1000</v>
       </c>
       <c r="N3" s="1">
-        <f t="shared" ref="N3:N74" si="0">C3-D3*20-E3*0.8-F3*0.6-H3*5+I3*10+J3/300+G3/1.3</f>
-        <v>13.846153846153847</v>
+        <f>C3-D3*20-E3*0.8-F3*0.6-H3*5+I3*10+J3/300+G3/1.3</f>
+        <v>8.8769230769230774</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="1">
-        <v>19</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="Q3" s="1"/>
       <c r="R3" s="1">
-        <f t="shared" ref="R3:R36" si="1">P3*0.024</f>
-        <v>0.45600000000000002</v>
+        <f>P3*0.022+0.02</f>
+        <v>0.23339999999999997</v>
       </c>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2">
-        <v>-3</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.35</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2">
+      <c r="C4" s="4">
+        <v>-6</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="4">
         <v>31</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2">
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="4">
         <v>1000</v>
       </c>
       <c r="N4" s="1">
-        <f t="shared" si="0"/>
-        <v>13.846153846153847</v>
+        <f t="shared" ref="N4:N74" si="0">C4-D4*20-E4*0.8-F4*0.6-H4*5+I4*10+J4/300+G4/1.3</f>
+        <v>10.046153846153846</v>
       </c>
       <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
+      <c r="P4" s="1">
+        <v>18.399999999999999</v>
+      </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="R4:R51" si="1">P4*0.022+0.02</f>
+        <v>0.42479999999999996</v>
       </c>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2">
-        <v>17</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2">
-        <v>500</v>
+      <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4">
+        <v>-10</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4">
+        <v>50</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="4">
+        <v>3000</v>
       </c>
       <c r="N5" s="1">
         <f t="shared" si="0"/>
-        <v>9.0769230769230766</v>
+        <v>10.46153846153846</v>
       </c>
       <c r="O5" s="1"/>
-      <c r="P5" s="1">
-        <v>11</v>
+      <c r="P5">
+        <v>44.6</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1">
-        <f>P5*0.024</f>
-        <v>0.26400000000000001</v>
+        <f t="shared" si="1"/>
+        <v>1.0011999999999999</v>
       </c>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2">
-        <v>-7</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2">
-        <v>50</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2">
-        <v>3000</v>
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="4">
+        <v>0</v>
       </c>
       <c r="N6" s="1">
         <f t="shared" si="0"/>
-        <v>17.46153846153846</v>
+        <v>-0.4</v>
       </c>
       <c r="O6" s="1"/>
-      <c r="P6" s="1">
-        <v>35</v>
-      </c>
+      <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1">
         <f t="shared" si="1"/>
-        <v>0.84</v>
+        <v>0.02</v>
       </c>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2">
-        <v>-7</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2">
-        <v>50</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2">
-        <v>3000</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
       <c r="N7" s="1">
         <f t="shared" si="0"/>
-        <v>17.46153846153846</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0.02</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="6">
+        <v>17</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="6">
+        <v>500</v>
       </c>
       <c r="N8" s="1">
         <f t="shared" si="0"/>
-        <v>-0.4</v>
+        <v>8.8769230769230774</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9">
-        <v>-8</v>
-      </c>
-      <c r="D9">
-        <v>0.3</v>
-      </c>
-      <c r="G9">
-        <v>23</v>
-      </c>
-      <c r="M9">
-        <v>1000</v>
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-10</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="6">
+        <v>50</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="6">
+        <v>3000</v>
       </c>
       <c r="N9" s="1">
         <f t="shared" si="0"/>
-        <v>3.6923076923076934</v>
+        <v>10.46153846153846</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10">
-        <v>-8</v>
-      </c>
-      <c r="D10">
-        <v>0.3</v>
-      </c>
-      <c r="G10">
-        <v>23</v>
-      </c>
-      <c r="M10">
+      <c r="A10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="6">
         <v>1000</v>
       </c>
       <c r="N10" s="1">
-        <f t="shared" si="0"/>
-        <v>3.6923076923076934</v>
+        <f>C10-D10*20-E10*0.8-F10*0.6-H10*5+I10*10+J10/300+G10/1.3</f>
+        <v>-0.4</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="N11" s="1"/>
+      <c r="A11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-8</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="6">
+        <v>23</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="6">
+        <v>1000</v>
+      </c>
+      <c r="N11" s="1">
+        <f t="shared" si="0"/>
+        <v>3.6923076923076934</v>
+      </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
+      <c r="R11" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0.02</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
       <c r="N12" s="1">
         <f t="shared" si="0"/>
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="2">
-        <v>-5</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2">
-        <v>18</v>
-      </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2">
-        <v>1000</v>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4">
+        <v>17</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="4">
+        <v>500</v>
       </c>
       <c r="N13" s="1">
-        <f t="shared" si="0"/>
-        <v>4.6461538461538456</v>
+        <f>C13-D13*20-E13*0.8-F13*0.6-H13*5+I13*10+J13/300+G13/1.3</f>
+        <v>9.0769230769230766</v>
       </c>
       <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
+      <c r="P13" s="1">
+        <v>11</v>
+      </c>
       <c r="Q13" s="1"/>
       <c r="R13" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="2">
+    <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="4">
         <v>-3</v>
       </c>
-      <c r="D14" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2">
-        <v>15</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2">
-        <v>500</v>
+      <c r="D14" s="4">
+        <v>0.35</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4">
+        <v>31</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="4">
+        <v>1000</v>
       </c>
       <c r="N14" s="1">
         <f t="shared" si="0"/>
-        <v>4.9384615384615387</v>
+        <v>13.846153846153847</v>
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2">
-        <v>10</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2">
-        <v>300</v>
+    <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="4">
+        <v>16</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4">
+        <v>29</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="4">
+        <v>1000</v>
       </c>
       <c r="N15" s="1">
-        <f t="shared" si="0"/>
-        <v>5.092307692307692</v>
+        <f>C15-D15*20-E15*0.8-F15*0.6-H15*5+I15*10+J15/300+G15/1.3</f>
+        <v>33.107692307692304</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
     </row>
-    <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="4">
+        <v>-7</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4">
+        <v>50</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="4">
+        <v>3000</v>
+      </c>
       <c r="N16" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17.46153846153846</v>
       </c>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2">
-        <v>0</v>
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="4">
+        <v>-8</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="4">
+        <v>23</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="4">
+        <v>1000</v>
       </c>
       <c r="N17" s="1">
         <f t="shared" si="0"/>
-        <v>-0.4</v>
+        <v>3.6923076923076934</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="2">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2">
-        <v>17</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2">
-        <v>0</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
       <c r="N18" s="1">
         <f t="shared" si="0"/>
-        <v>9.2769230769230759</v>
+        <v>0</v>
       </c>
       <c r="O18" s="1"/>
-      <c r="P18" s="1">
-        <v>10.5</v>
-      </c>
+      <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1">
         <f t="shared" si="1"/>
-        <v>0.252</v>
+        <v>0.02</v>
       </c>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="2">
-        <v>-2</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2">
-        <v>21</v>
-      </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2">
-        <v>2000</v>
+      <c r="A19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="4">
+        <v>0</v>
       </c>
       <c r="N19" s="1">
         <f t="shared" si="0"/>
-        <v>9.5538461538461519</v>
+        <v>-0.4</v>
       </c>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="2">
-        <v>-4</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.33</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2">
-        <v>30</v>
-      </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2">
-        <v>4000</v>
+      <c r="A20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.22</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="4">
+        <v>18</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="4">
+        <v>1000</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" si="0"/>
-        <v>12.476923076923075</v>
+        <v>9.4461538461538446</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+      <c r="A21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.19</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="4">
+        <v>15</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="4">
+        <v>500</v>
+      </c>
       <c r="N21" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.7384615384615394</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="4">
-        <v>0</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0.36</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4">
-        <v>30</v>
-      </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4">
-        <v>500</v>
+      <c r="A22" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="10">
+        <v>5</v>
+      </c>
+      <c r="D22" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="10">
+        <v>10</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="10">
+        <v>0</v>
       </c>
       <c r="N22" s="1">
         <f t="shared" si="0"/>
-        <v>15.876923076923077</v>
+        <v>9.8923076923076909</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
     </row>
     <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
       <c r="N23" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1398,25 +1476,33 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
     </row>
     <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0.02</v>
-      </c>
-      <c r="M24">
+      <c r="A24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="6">
         <v>0</v>
       </c>
       <c r="N24" s="1">
@@ -1428,111 +1514,149 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0.34</v>
-      </c>
-      <c r="G25">
-        <v>30</v>
-      </c>
-      <c r="M25">
+      <c r="A25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="6">
+        <v>17</v>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="6">
         <v>0</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" si="0"/>
-        <v>16.276923076923076</v>
+        <v>8.6769230769230763</v>
       </c>
       <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
+      <c r="P25" s="1">
+        <v>10.6</v>
+      </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.25319999999999998</v>
       </c>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26">
-        <v>9</v>
-      </c>
-      <c r="D26">
-        <v>0.13</v>
-      </c>
-      <c r="G26">
-        <v>10</v>
-      </c>
-      <c r="M26">
-        <v>200</v>
+      <c r="A26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-2</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="6">
+        <v>21</v>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="6">
+        <v>2000</v>
       </c>
       <c r="N26" s="1">
         <f t="shared" si="0"/>
-        <v>14.092307692307692</v>
+        <v>8.5538461538461519</v>
       </c>
       <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
+      <c r="P26" s="1">
+        <v>13.2</v>
+      </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.31040000000000001</v>
       </c>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
     </row>
     <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27">
+      <c r="A27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="6">
         <v>-6</v>
       </c>
-      <c r="D27">
-        <v>0.65</v>
-      </c>
-      <c r="G27">
-        <v>50</v>
-      </c>
-      <c r="M27">
-        <v>3000</v>
+      <c r="D27" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="6">
+        <v>30</v>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="6">
+        <v>4000</v>
       </c>
       <c r="N27" s="1">
         <f t="shared" si="0"/>
-        <v>19.46153846153846</v>
+        <v>9.0769230769230766</v>
       </c>
       <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
+      <c r="P27">
+        <v>19</v>
+      </c>
       <c r="Q27" s="1"/>
       <c r="R27" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
     </row>
     <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
       <c r="N28" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1542,644 +1666,882 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
     </row>
     <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>0.02</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
+      <c r="A29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="6">
+        <v>30</v>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="6">
+        <v>500</v>
       </c>
       <c r="N29" s="1">
         <f t="shared" si="0"/>
-        <v>-0.4</v>
+        <v>15.476923076923077</v>
       </c>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
       <c r="R29" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
     </row>
     <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0.34</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2">
-        <v>30</v>
-      </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2">
-        <v>0</v>
-      </c>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
       <c r="N30" s="1">
         <f t="shared" si="0"/>
-        <v>16.276923076923076</v>
+        <v>0</v>
       </c>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
     </row>
     <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0.36</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2">
-        <v>30</v>
-      </c>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2">
-        <v>500</v>
+      <c r="A31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="4">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="4">
+        <v>0</v>
       </c>
       <c r="N31" s="1">
         <f t="shared" si="0"/>
-        <v>16.876923076923077</v>
+        <v>-0.4</v>
       </c>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1">
-        <f>P31*0.024</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>0.02</v>
       </c>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
     </row>
     <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="2">
-        <v>-9</v>
-      </c>
-      <c r="D32" s="2">
-        <v>0.68</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2">
-        <v>50</v>
-      </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2">
-        <v>3000</v>
+      <c r="A32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="4">
+        <v>0</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0.34</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="4">
+        <v>30</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="4">
+        <v>0</v>
       </c>
       <c r="N32" s="1">
         <f t="shared" si="0"/>
-        <v>15.861538461538458</v>
+        <v>16.276923076923076</v>
       </c>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
     </row>
     <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
+      <c r="A33" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="4">
+        <v>9</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="4">
+        <v>10</v>
+      </c>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="4">
+        <v>200</v>
+      </c>
       <c r="N33" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13.692307692307692</v>
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
     </row>
     <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="2">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2">
-        <v>25</v>
-      </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2">
-        <v>500</v>
+      <c r="A34" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="4">
+        <v>-9</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="4">
+        <v>50</v>
+      </c>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="4">
+        <v>3000</v>
       </c>
       <c r="N34" s="1">
         <f t="shared" si="0"/>
-        <v>13.23076923076923</v>
+        <v>12.46153846153846</v>
       </c>
       <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
+      <c r="P34" s="1">
+        <v>42</v>
+      </c>
       <c r="Q34" s="1"/>
       <c r="R34" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
     </row>
     <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="2">
-        <v>-4</v>
-      </c>
-      <c r="D35" s="2">
-        <v>0.38</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2">
-        <v>32</v>
-      </c>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2">
-        <v>750</v>
-      </c>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
       <c r="N35" s="1">
         <f t="shared" si="0"/>
-        <v>13.015384615384614</v>
+        <v>0</v>
       </c>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
     </row>
     <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" s="2">
-        <v>-10</v>
-      </c>
-      <c r="D36" s="2">
-        <v>0.46</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2">
-        <v>40</v>
-      </c>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2">
-        <v>1000</v>
+      <c r="A36" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="4">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="4">
+        <v>0</v>
       </c>
       <c r="N36" s="1">
         <f t="shared" si="0"/>
-        <v>11.569230769230764</v>
+        <v>-0.4</v>
       </c>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
     </row>
     <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
+      <c r="A37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="4">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0.35</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="4">
+        <v>30</v>
+      </c>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="4">
+        <v>0</v>
+      </c>
       <c r="N37" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.076923076923077</v>
       </c>
       <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
+      <c r="P37">
+        <v>17</v>
+      </c>
       <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
+      <c r="R37" s="1">
+        <f t="shared" si="1"/>
+        <v>0.39400000000000002</v>
+      </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
     </row>
     <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>0.36</v>
-      </c>
-      <c r="G38">
-        <v>32</v>
-      </c>
-      <c r="M38">
+      <c r="A38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="6">
+        <v>1</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0.37</v>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="6">
+        <v>30</v>
+      </c>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="6">
         <v>500</v>
       </c>
       <c r="N38" s="1">
         <f t="shared" si="0"/>
-        <v>17.415384615384614</v>
+        <v>16.676923076923075</v>
       </c>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
+      <c r="R38" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
     </row>
     <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39">
-        <v>7</v>
-      </c>
-      <c r="D39">
-        <v>0.23</v>
-      </c>
-      <c r="F39">
-        <v>-2</v>
-      </c>
-      <c r="G39">
-        <v>20</v>
-      </c>
-      <c r="M39">
-        <v>400</v>
+      <c r="A39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-9</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0.83</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="6">
+        <v>50</v>
+      </c>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="6">
+        <v>3000</v>
       </c>
       <c r="N39" s="1">
         <f t="shared" si="0"/>
-        <v>18.984615384615381</v>
+        <v>12.861538461538462</v>
       </c>
       <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
+      <c r="P39" s="1">
+        <v>40</v>
+      </c>
       <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
+      <c r="R39" s="1">
+        <f t="shared" si="1"/>
+        <v>0.89999999999999991</v>
+      </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
     </row>
     <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40">
-        <v>14</v>
-      </c>
-      <c r="D40">
-        <v>0.12</v>
-      </c>
-      <c r="F40">
-        <v>-4</v>
-      </c>
-      <c r="G40">
-        <v>10</v>
-      </c>
-      <c r="M40">
-        <v>200</v>
-      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
       <c r="N40" s="1">
         <f t="shared" si="0"/>
-        <v>21.692307692307693</v>
+        <v>0</v>
       </c>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
-      <c r="R40" s="1"/>
+      <c r="R40" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
     </row>
     <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>71</v>
-      </c>
-      <c r="B41" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41">
-        <v>-20</v>
-      </c>
-      <c r="D41">
-        <v>0.6</v>
-      </c>
-      <c r="G41">
-        <v>50</v>
-      </c>
-      <c r="H41">
-        <v>0.05</v>
-      </c>
-      <c r="M41">
-        <v>5000</v>
+      <c r="A41" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0.34</v>
+      </c>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="6">
+        <v>25</v>
+      </c>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="6">
+        <v>500</v>
       </c>
       <c r="N41" s="1">
         <f t="shared" si="0"/>
-        <v>6.2115384615384599</v>
+        <v>12.430769230769229</v>
       </c>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
+      <c r="R41" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
     </row>
     <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>73</v>
-      </c>
-      <c r="B42" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42">
-        <v>-5</v>
-      </c>
-      <c r="D42">
-        <v>0.11</v>
-      </c>
-      <c r="G42">
-        <v>10</v>
-      </c>
-      <c r="M42">
-        <v>1000</v>
+      <c r="A42" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-4</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="6">
+        <v>32</v>
+      </c>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="6">
+        <v>750</v>
       </c>
       <c r="N42" s="1">
         <f t="shared" si="0"/>
-        <v>0.49230769230769145</v>
+        <v>12.815384615384612</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
+      <c r="R42" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
     </row>
     <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>75</v>
-      </c>
-      <c r="B43" t="s">
-        <v>76</v>
-      </c>
-      <c r="C43">
-        <v>-45</v>
-      </c>
-      <c r="D43">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E43">
-        <v>20</v>
-      </c>
-      <c r="F43">
-        <v>20</v>
-      </c>
-      <c r="G43">
-        <v>50</v>
-      </c>
-      <c r="H43">
-        <v>0.05</v>
-      </c>
-      <c r="M43">
-        <v>5000</v>
+      <c r="A43" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-8</v>
+      </c>
+      <c r="D43" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="6">
+        <v>40</v>
+      </c>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="6">
+        <v>1000</v>
       </c>
       <c r="N43" s="1">
         <f t="shared" si="0"/>
-        <v>-46.188461538461546</v>
+        <v>12.769230769230766</v>
       </c>
       <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
+      <c r="P43" s="1">
+        <v>22</v>
+      </c>
       <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
+      <c r="R43" s="1">
+        <f t="shared" si="1"/>
+        <v>0.504</v>
+      </c>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
     </row>
     <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44">
-        <v>-2</v>
-      </c>
-      <c r="D44">
-        <v>0.1</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7"/>
       <c r="N44" s="1">
         <f t="shared" si="0"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
+      <c r="R44" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
     </row>
     <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0</v>
+      </c>
+      <c r="D45" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="6">
+        <v>32</v>
+      </c>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="6">
+        <v>0</v>
+      </c>
       <c r="N45" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.815384615384612</v>
       </c>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
+      <c r="R45" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
     </row>
     <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" s="6">
+        <v>6</v>
+      </c>
+      <c r="D46" s="6">
+        <v>0.27</v>
+      </c>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="6">
+        <v>20</v>
+      </c>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="6">
+        <v>400</v>
+      </c>
       <c r="N46" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15.984615384615383</v>
       </c>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
+      <c r="R46" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
     </row>
     <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="6">
+        <v>10</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0.13</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="6">
+        <v>10</v>
+      </c>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="6">
+        <v>200</v>
+      </c>
       <c r="N47" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15.092307692307692</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
+      <c r="R47" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
     </row>
     <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-15</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="6">
+        <v>50</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="6">
+        <v>5000</v>
+      </c>
       <c r="N48" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.0615384615384613</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
+      <c r="R48" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
     </row>
-    <row r="49" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-6</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="6">
+        <v>10</v>
+      </c>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="6">
+        <v>1000</v>
+      </c>
       <c r="N49" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-0.70769230769230873</v>
       </c>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
+      <c r="R49" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
     </row>
-    <row r="50" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-40</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6">
+        <v>50</v>
+      </c>
+      <c r="H50" s="6"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="6">
+        <v>5000</v>
+      </c>
       <c r="N50" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-12.938461538461539</v>
       </c>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
+      <c r="R50" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
     </row>
-    <row r="51" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-2</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="6">
+        <v>0</v>
+      </c>
       <c r="N51" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
-      <c r="R51" s="1"/>
+      <c r="R51" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
     </row>
-    <row r="52" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N52" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2191,7 +2553,7 @@
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
     </row>
-    <row r="53" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N53" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2203,7 +2565,7 @@
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
     </row>
-    <row r="54" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N54" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2215,7 +2577,7 @@
       <c r="S54" s="1"/>
       <c r="T54" s="1"/>
     </row>
-    <row r="55" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N55" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2227,7 +2589,7 @@
       <c r="S55" s="1"/>
       <c r="T55" s="1"/>
     </row>
-    <row r="56" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N56" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2239,7 +2601,7 @@
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
     </row>
-    <row r="57" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N57" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2251,7 +2613,7 @@
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
     </row>
-    <row r="58" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N58" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2263,7 +2625,7 @@
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
     </row>
-    <row r="59" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N59" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2275,7 +2637,7 @@
       <c r="S59" s="1"/>
       <c r="T59" s="1"/>
     </row>
-    <row r="60" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N60" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2287,7 +2649,7 @@
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
     </row>
-    <row r="61" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N61" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2299,7 +2661,7 @@
       <c r="S61" s="1"/>
       <c r="T61" s="1"/>
     </row>
-    <row r="62" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N62" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2311,7 +2673,7 @@
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
     </row>
-    <row r="63" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N63" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2323,7 +2685,7 @@
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
     </row>
-    <row r="64" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N64" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3380,7 +3742,6 @@
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/changes/9mm-mags.xlsx
+++ b/changes/9mm-mags.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2BA538-C904-47E1-9AAC-8F865DC057B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7496E0F7-6453-43BB-A302-224862613415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -330,7 +330,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,21 +340,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -377,19 +362,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -605,11 +580,10 @@
   <dimension ref="A1:T998"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46" style="2" customWidth="1"/>
-    <col min="2" max="2" width="48" style="2" customWidth="1"/>
-    <col min="3" max="18" width="8.7109375" style="2" customWidth="1"/>
-    <col min="19" max="20" width="6.7109375" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="14.42578125" style="2"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="20" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -637,82 +611,75 @@
       <c r="T1" s="1"/>
     </row>
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>0.21</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="4">
+      <c r="G3">
         <v>17</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="4">
+      <c r="M3">
         <v>1000</v>
       </c>
       <c r="N3" s="1">
@@ -732,29 +699,22 @@
       <c r="T3" s="1"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>-6</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4">
         <v>0.39</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4">
+      <c r="G4">
         <v>31</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="4">
+      <c r="M4">
         <v>1000</v>
       </c>
       <c r="N4" s="1">
@@ -774,29 +734,22 @@
       <c r="T4" s="1"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>-10</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5">
         <v>0.9</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="4">
+      <c r="G5">
         <v>50</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="4">
+      <c r="M5">
         <v>3000</v>
       </c>
       <c r="N5" s="1">
@@ -816,27 +769,19 @@
       <c r="T5" s="1"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="4">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0.02</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
       <c r="N6" s="1">
@@ -854,19 +799,6 @@
       <c r="T6" s="1"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
       <c r="N7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -882,29 +814,22 @@
       <c r="T7" s="1"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>0.21</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="6">
+      <c r="G8">
         <v>17</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="6">
+      <c r="M8">
         <v>500</v>
       </c>
       <c r="N8" s="1">
@@ -922,34 +847,27 @@
       <c r="T8" s="1"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="6">
-        <v>-10</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9">
+        <v>-6</v>
+      </c>
+      <c r="D9">
         <v>0.9</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="6">
+      <c r="G9">
         <v>50</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="6">
+      <c r="M9">
         <v>3000</v>
       </c>
       <c r="N9" s="1">
         <f t="shared" si="0"/>
-        <v>10.46153846153846</v>
+        <v>14.46153846153846</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -962,27 +880,19 @@
       <c r="T9" s="1"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="6">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="6">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0.02</v>
+      </c>
+      <c r="M10">
         <v>1000</v>
       </c>
       <c r="N10" s="1">
@@ -1000,29 +910,22 @@
       <c r="T10" s="1"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11">
         <v>-8</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11">
         <v>0.3</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="6">
+      <c r="G11">
         <v>23</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="6">
+      <c r="M11">
         <v>1000</v>
       </c>
       <c r="N11" s="1">
@@ -1040,17 +943,6 @@
       <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
       <c r="N12" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1066,29 +958,22 @@
       <c r="T12" s="1"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="4">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>0.2</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="4">
+      <c r="G13">
         <v>17</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="4">
+      <c r="M13">
         <v>500</v>
       </c>
       <c r="N13" s="1">
@@ -1108,29 +993,22 @@
       <c r="T13" s="1"/>
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14">
         <v>-3</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14">
         <v>0.35</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="4">
+      <c r="G14">
         <v>31</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="4">
+      <c r="M14">
         <v>1000</v>
       </c>
       <c r="N14" s="1">
@@ -1148,29 +1026,22 @@
       <c r="T14" s="1"/>
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15">
         <v>16</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15">
         <v>0.26</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="4">
+      <c r="G15">
         <v>29</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="4">
+      <c r="M15">
         <v>1000</v>
       </c>
       <c r="N15" s="1">
@@ -1188,29 +1059,22 @@
       <c r="T15" s="1"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16">
         <v>-7</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16">
         <v>0.7</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="4">
+      <c r="G16">
         <v>50</v>
       </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="4">
+      <c r="M16">
         <v>3000</v>
       </c>
       <c r="N16" s="1">
@@ -1228,29 +1092,22 @@
       <c r="T16" s="1"/>
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17">
         <v>-8</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17">
         <v>0.3</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="4">
+      <c r="G17">
         <v>23</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="4">
+      <c r="M17">
         <v>1000</v>
       </c>
       <c r="N17" s="1">
@@ -1268,19 +1125,6 @@
       <c r="T17" s="1"/>
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
       <c r="N18" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1296,27 +1140,19 @@
       <c r="T18" s="1"/>
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="4">
-        <v>0</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="4">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0.02</v>
+      </c>
+      <c r="M19">
         <v>0</v>
       </c>
       <c r="N19" s="1">
@@ -1334,29 +1170,22 @@
       <c r="T19" s="1"/>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="4">
-        <v>0</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
         <v>0.22</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="4">
+      <c r="G20">
         <v>18</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="4">
+      <c r="M20">
         <v>1000</v>
       </c>
       <c r="N20" s="1">
@@ -1374,29 +1203,22 @@
       <c r="T20" s="1"/>
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21">
         <v>2</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21">
         <v>0.19</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="4">
+      <c r="G21">
         <v>15</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="4">
+      <c r="M21">
         <v>500</v>
       </c>
       <c r="N21" s="1">
@@ -1414,29 +1236,22 @@
       <c r="T21" s="1"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22">
         <v>5</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="10">
+      <c r="G22">
         <v>10</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="10">
+      <c r="M22">
         <v>0</v>
       </c>
       <c r="N22" s="1">
@@ -1454,19 +1269,6 @@
       <c r="T22" s="1"/>
     </row>
     <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
       <c r="N23" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1482,27 +1284,19 @@
       <c r="T23" s="1"/>
     </row>
     <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="6">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="6">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0.02</v>
+      </c>
+      <c r="M24">
         <v>0</v>
       </c>
       <c r="N24" s="1">
@@ -1520,29 +1314,22 @@
       <c r="T24" s="1"/>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="6">
-        <v>0</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
         <v>0.22</v>
       </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="6">
+      <c r="G25">
         <v>17</v>
       </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="6">
+      <c r="M25">
         <v>0</v>
       </c>
       <c r="N25" s="1">
@@ -1562,29 +1349,22 @@
       <c r="T25" s="1"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="A26" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26">
         <v>-2</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26">
         <v>0.28000000000000003</v>
       </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="6">
+      <c r="G26">
         <v>21</v>
       </c>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="6">
+      <c r="M26">
         <v>2000</v>
       </c>
       <c r="N26" s="1">
@@ -1604,29 +1384,22 @@
       <c r="T26" s="1"/>
     </row>
     <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27">
         <v>-6</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27">
         <v>0.4</v>
       </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="6">
+      <c r="G27">
         <v>30</v>
       </c>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="6">
+      <c r="M27">
         <v>4000</v>
       </c>
       <c r="N27" s="1">
@@ -1646,17 +1419,6 @@
       <c r="T27" s="1"/>
     </row>
     <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
       <c r="N28" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1672,29 +1434,22 @@
       <c r="T28" s="1"/>
     </row>
     <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="A29" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="6">
-        <v>0</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
         <v>0.38</v>
       </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="6">
+      <c r="G29">
         <v>30</v>
       </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="6">
+      <c r="M29">
         <v>500</v>
       </c>
       <c r="N29" s="1">
@@ -1712,19 +1467,6 @@
       <c r="T29" s="1"/>
     </row>
     <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
       <c r="N30" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1740,27 +1482,19 @@
       <c r="T30" s="1"/>
     </row>
     <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="A31" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="4">
-        <v>0</v>
-      </c>
-      <c r="D31" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="4">
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0.02</v>
+      </c>
+      <c r="M31">
         <v>0</v>
       </c>
       <c r="N31" s="1">
@@ -1778,29 +1512,22 @@
       <c r="T31" s="1"/>
     </row>
     <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="A32" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="4">
-        <v>0</v>
-      </c>
-      <c r="D32" s="4">
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
         <v>0.34</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="4">
+      <c r="G32">
         <v>30</v>
       </c>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="4">
+      <c r="M32">
         <v>0</v>
       </c>
       <c r="N32" s="1">
@@ -1818,29 +1545,22 @@
       <c r="T32" s="1"/>
     </row>
     <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="A33" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33">
         <v>9</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33">
         <v>0.15</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="4">
+      <c r="G33">
         <v>10</v>
       </c>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="4">
+      <c r="M33">
         <v>200</v>
       </c>
       <c r="N33" s="1">
@@ -1858,34 +1578,27 @@
       <c r="T33" s="1"/>
     </row>
     <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="A34" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="4">
-        <v>-9</v>
-      </c>
-      <c r="D34" s="4">
+      <c r="C34">
+        <v>-6</v>
+      </c>
+      <c r="D34">
         <v>0.85</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="4">
+      <c r="G34">
         <v>50</v>
       </c>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="4">
+      <c r="M34">
         <v>3000</v>
       </c>
       <c r="N34" s="1">
         <f t="shared" si="0"/>
-        <v>12.46153846153846</v>
+        <v>15.46153846153846</v>
       </c>
       <c r="O34" s="1"/>
       <c r="P34" s="1">
@@ -1900,19 +1613,6 @@
       <c r="T34" s="1"/>
     </row>
     <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
       <c r="N35" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1928,27 +1628,19 @@
       <c r="T35" s="1"/>
     </row>
     <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="A36" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="4">
-        <v>0</v>
-      </c>
-      <c r="D36" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="4">
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0.02</v>
+      </c>
+      <c r="M36">
         <v>0</v>
       </c>
       <c r="N36" s="1">
@@ -1966,29 +1658,22 @@
       <c r="T36" s="1"/>
     </row>
     <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="A37" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="4">
-        <v>0</v>
-      </c>
-      <c r="D37" s="4">
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
         <v>0.35</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="4">
+      <c r="G37">
         <v>30</v>
       </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="4">
+      <c r="M37">
         <v>0</v>
       </c>
       <c r="N37" s="1">
@@ -2008,29 +1693,22 @@
       <c r="T37" s="1"/>
     </row>
     <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="A38" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38">
         <v>1</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38">
         <v>0.37</v>
       </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="6">
+      <c r="G38">
         <v>30</v>
       </c>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="6">
+      <c r="M38">
         <v>500</v>
       </c>
       <c r="N38" s="1">
@@ -2048,34 +1726,27 @@
       <c r="T38" s="1"/>
     </row>
     <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="6">
-        <v>-9</v>
-      </c>
-      <c r="D39" s="6">
+      <c r="C39">
+        <v>-6</v>
+      </c>
+      <c r="D39">
         <v>0.83</v>
       </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="6">
+      <c r="G39">
         <v>50</v>
       </c>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="6">
+      <c r="M39">
         <v>3000</v>
       </c>
       <c r="N39" s="1">
         <f t="shared" si="0"/>
-        <v>12.861538461538462</v>
+        <v>15.861538461538462</v>
       </c>
       <c r="O39" s="1"/>
       <c r="P39" s="1">
@@ -2090,17 +1761,6 @@
       <c r="T39" s="1"/>
     </row>
     <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
       <c r="N40" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2116,29 +1776,22 @@
       <c r="T40" s="1"/>
     </row>
     <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+      <c r="A41" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" t="s">
         <v>78</v>
       </c>
-      <c r="C41" s="6">
-        <v>0</v>
-      </c>
-      <c r="D41" s="6">
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
         <v>0.34</v>
       </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="6">
+      <c r="G41">
         <v>25</v>
       </c>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="6">
+      <c r="M41">
         <v>500</v>
       </c>
       <c r="N41" s="1">
@@ -2156,29 +1809,22 @@
       <c r="T41" s="1"/>
     </row>
     <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="A42" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42">
         <v>-4</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42">
         <v>0.39</v>
       </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="6">
+      <c r="G42">
         <v>32</v>
       </c>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="6">
+      <c r="M42">
         <v>750</v>
       </c>
       <c r="N42" s="1">
@@ -2196,29 +1842,22 @@
       <c r="T42" s="1"/>
     </row>
     <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="A43" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43">
         <v>-8</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43">
         <v>0.5</v>
       </c>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="6">
+      <c r="G43">
         <v>40</v>
       </c>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="6">
+      <c r="M43">
         <v>1000</v>
       </c>
       <c r="N43" s="1">
@@ -2238,17 +1877,6 @@
       <c r="T43" s="1"/>
     </row>
     <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
       <c r="N44" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2264,29 +1892,22 @@
       <c r="T44" s="1"/>
     </row>
     <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="A45" t="s">
         <v>83</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" t="s">
         <v>84</v>
       </c>
-      <c r="C45" s="6">
-        <v>0</v>
-      </c>
-      <c r="D45" s="6">
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
         <v>0.39</v>
       </c>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="6">
+      <c r="G45">
         <v>32</v>
       </c>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="6">
+      <c r="M45">
         <v>0</v>
       </c>
       <c r="N45" s="1">
@@ -2304,29 +1925,22 @@
       <c r="T45" s="1"/>
     </row>
     <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="A46" t="s">
         <v>85</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" t="s">
         <v>86</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46">
         <v>6</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46">
         <v>0.27</v>
       </c>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="6">
+      <c r="G46">
         <v>20</v>
       </c>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="6">
+      <c r="M46">
         <v>400</v>
       </c>
       <c r="N46" s="1">
@@ -2344,29 +1958,22 @@
       <c r="T46" s="1"/>
     </row>
     <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="A47" t="s">
         <v>87</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" t="s">
         <v>88</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47">
         <v>10</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47">
         <v>0.13</v>
       </c>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="6">
+      <c r="G47">
         <v>10</v>
       </c>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="6">
+      <c r="M47">
         <v>200</v>
       </c>
       <c r="N47" s="1">
@@ -2384,29 +1991,22 @@
       <c r="T47" s="1"/>
     </row>
     <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="A48" t="s">
         <v>89</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" t="s">
         <v>90</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48">
         <v>-15</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48">
         <v>0.77</v>
       </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="6">
+      <c r="G48">
         <v>50</v>
       </c>
-      <c r="H48" s="6"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="6">
+      <c r="M48">
         <v>5000</v>
       </c>
       <c r="N48" s="1">
@@ -2424,29 +2024,22 @@
       <c r="T48" s="1"/>
     </row>
     <row r="49" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+      <c r="A49" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" t="s">
         <v>92</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49">
         <v>-6</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49">
         <v>0.12</v>
       </c>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="6">
+      <c r="G49">
         <v>10</v>
       </c>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="6">
+      <c r="M49">
         <v>1000</v>
       </c>
       <c r="N49" s="1">
@@ -2464,34 +2057,27 @@
       <c r="T49" s="1"/>
     </row>
     <row r="50" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="A50" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" t="s">
         <v>94</v>
       </c>
-      <c r="C50" s="6">
-        <v>-40</v>
-      </c>
-      <c r="D50" s="6">
+      <c r="C50">
+        <v>-45</v>
+      </c>
+      <c r="D50">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6">
+      <c r="G50">
         <v>50</v>
       </c>
-      <c r="H50" s="6"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="6">
+      <c r="M50">
         <v>5000</v>
       </c>
       <c r="N50" s="1">
         <f t="shared" si="0"/>
-        <v>-12.938461538461539</v>
+        <v>-17.938461538461539</v>
       </c>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
@@ -2504,27 +2090,19 @@
       <c r="T50" s="1"/>
     </row>
     <row r="51" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="A51" t="s">
         <v>95</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" t="s">
         <v>96</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51">
         <v>-2</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51">
         <v>0.1</v>
       </c>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="6">
+      <c r="M51">
         <v>0</v>
       </c>
       <c r="N51" s="1">

--- a/changes/9mm-mags.xlsx
+++ b/changes/9mm-mags.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yifan/Documents/deadline-dev/deadline-balancing/changes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7496E0F7-6453-43BB-A302-224862613415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BA2BD3-FF34-6149-BC1A-C76A46F50FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="9mm-mags" sheetId="1" r:id="rId1"/>
@@ -215,9 +215,6 @@
     <t>hk_ump9_9x19_30r_mag</t>
   </si>
   <si>
-    <t>UMC-9 9x19 30R</t>
-  </si>
-  <si>
     <t>kazarov_pp-19-01_mag_bottom_plate</t>
   </si>
   <si>
@@ -324,6 +321,9 @@
   </si>
   <si>
     <t>Custom Hart SMG 9x19</t>
+  </si>
+  <si>
+    <t>UMK-9 9x19 30R</t>
   </si>
 </sst>
 </file>
@@ -340,6 +340,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -578,15 +579,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T998"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="20" width="6.7109375" customWidth="1"/>
+    <col min="3" max="18" width="8.6640625" customWidth="1"/>
+    <col min="19" max="20" width="6.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
@@ -610,7 +611,7 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -663,7 +664,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -698,7 +699,7 @@
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -733,7 +734,7 @@
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -741,10 +742,10 @@
         <v>23</v>
       </c>
       <c r="C5">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="D5">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G5">
         <v>50</v>
@@ -754,7 +755,7 @@
       </c>
       <c r="N5" s="1">
         <f t="shared" si="0"/>
-        <v>10.46153846153846</v>
+        <v>15.46153846153846</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5">
@@ -768,7 +769,7 @@
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -798,7 +799,7 @@
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -813,7 +814,7 @@
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -846,7 +847,7 @@
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -857,7 +858,7 @@
         <v>-6</v>
       </c>
       <c r="D9">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G9">
         <v>50</v>
@@ -867,7 +868,7 @@
       </c>
       <c r="N9" s="1">
         <f t="shared" si="0"/>
-        <v>14.46153846153846</v>
+        <v>15.46153846153846</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -879,7 +880,7 @@
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -909,7 +910,7 @@
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -942,7 +943,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N12" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -957,7 +958,7 @@
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -992,7 +993,7 @@
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -1025,7 +1026,7 @@
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -1058,7 +1059,7 @@
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -1091,7 +1092,7 @@
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -1124,7 +1125,7 @@
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
     </row>
-    <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N18" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1139,7 +1140,7 @@
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
     </row>
-    <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -1169,7 +1170,7 @@
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
     </row>
-    <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -1202,7 +1203,7 @@
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
     </row>
-    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -1235,7 +1236,7 @@
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1268,7 +1269,7 @@
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
     </row>
-    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N23" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1283,7 +1284,7 @@
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
     </row>
-    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1313,7 +1314,7 @@
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1348,7 +1349,7 @@
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1383,7 +1384,7 @@
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
     </row>
-    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>57</v>
       </c>
@@ -1418,7 +1419,7 @@
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
     </row>
-    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N28" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1433,12 +1434,12 @@
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
     </row>
-    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B29" t="s">
-        <v>60</v>
+      <c r="B29" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -1466,7 +1467,7 @@
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
     </row>
-    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N30" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1481,12 +1482,12 @@
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
     </row>
-    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
         <v>61</v>
-      </c>
-      <c r="B31" t="s">
-        <v>62</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1511,12 +1512,12 @@
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
     </row>
-    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
         <v>63</v>
-      </c>
-      <c r="B32" t="s">
-        <v>64</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -1544,12 +1545,12 @@
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
     </row>
-    <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
         <v>65</v>
-      </c>
-      <c r="B33" t="s">
-        <v>66</v>
       </c>
       <c r="C33">
         <v>9</v>
@@ -1577,12 +1578,12 @@
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
     </row>
-    <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
         <v>67</v>
-      </c>
-      <c r="B34" t="s">
-        <v>68</v>
       </c>
       <c r="C34">
         <v>-6</v>
@@ -1612,7 +1613,7 @@
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
     </row>
-    <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N35" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1627,12 +1628,12 @@
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
     </row>
-    <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
         <v>69</v>
-      </c>
-      <c r="B36" t="s">
-        <v>70</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1657,12 +1658,12 @@
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
     </row>
-    <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" t="s">
         <v>71</v>
-      </c>
-      <c r="B37" t="s">
-        <v>72</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -1692,12 +1693,12 @@
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
     </row>
-    <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" t="s">
         <v>73</v>
-      </c>
-      <c r="B38" t="s">
-        <v>74</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1725,12 +1726,12 @@
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
     </row>
-    <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
         <v>75</v>
-      </c>
-      <c r="B39" t="s">
-        <v>76</v>
       </c>
       <c r="C39">
         <v>-6</v>
@@ -1760,7 +1761,7 @@
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
     </row>
-    <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N40" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1775,12 +1776,12 @@
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
     </row>
-    <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
         <v>77</v>
-      </c>
-      <c r="B41" t="s">
-        <v>78</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -1808,12 +1809,12 @@
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
     </row>
-    <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
         <v>79</v>
-      </c>
-      <c r="B42" t="s">
-        <v>80</v>
       </c>
       <c r="C42">
         <v>-4</v>
@@ -1841,12 +1842,12 @@
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
     </row>
-    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" t="s">
         <v>81</v>
-      </c>
-      <c r="B43" t="s">
-        <v>82</v>
       </c>
       <c r="C43">
         <v>-8</v>
@@ -1876,7 +1877,7 @@
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
     </row>
-    <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N44" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1891,12 +1892,12 @@
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
     </row>
-    <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" t="s">
         <v>83</v>
-      </c>
-      <c r="B45" t="s">
-        <v>84</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -1924,12 +1925,12 @@
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
     </row>
-    <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" t="s">
         <v>85</v>
-      </c>
-      <c r="B46" t="s">
-        <v>86</v>
       </c>
       <c r="C46">
         <v>6</v>
@@ -1957,12 +1958,12 @@
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
     </row>
-    <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" t="s">
         <v>87</v>
-      </c>
-      <c r="B47" t="s">
-        <v>88</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -1990,12 +1991,12 @@
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
     </row>
-    <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48" t="s">
         <v>89</v>
-      </c>
-      <c r="B48" t="s">
-        <v>90</v>
       </c>
       <c r="C48">
         <v>-15</v>
@@ -2023,12 +2024,12 @@
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
     </row>
-    <row r="49" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" t="s">
         <v>91</v>
-      </c>
-      <c r="B49" t="s">
-        <v>92</v>
       </c>
       <c r="C49">
         <v>-6</v>
@@ -2056,12 +2057,12 @@
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
     </row>
-    <row r="50" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" t="s">
         <v>93</v>
-      </c>
-      <c r="B50" t="s">
-        <v>94</v>
       </c>
       <c r="C50">
         <v>-45</v>
@@ -2089,12 +2090,12 @@
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
     </row>
-    <row r="51" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" t="s">
         <v>95</v>
-      </c>
-      <c r="B51" t="s">
-        <v>96</v>
       </c>
       <c r="C51">
         <v>-2</v>
@@ -2119,7 +2120,7 @@
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
     </row>
-    <row r="52" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N52" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2131,7 +2132,7 @@
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
     </row>
-    <row r="53" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N53" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2143,7 +2144,7 @@
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
     </row>
-    <row r="54" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N54" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2155,7 +2156,7 @@
       <c r="S54" s="1"/>
       <c r="T54" s="1"/>
     </row>
-    <row r="55" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N55" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2167,7 +2168,7 @@
       <c r="S55" s="1"/>
       <c r="T55" s="1"/>
     </row>
-    <row r="56" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N56" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2179,7 +2180,7 @@
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
     </row>
-    <row r="57" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N57" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2191,7 +2192,7 @@
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
     </row>
-    <row r="58" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N58" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2203,7 +2204,7 @@
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
     </row>
-    <row r="59" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N59" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2215,7 +2216,7 @@
       <c r="S59" s="1"/>
       <c r="T59" s="1"/>
     </row>
-    <row r="60" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N60" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2227,7 +2228,7 @@
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
     </row>
-    <row r="61" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N61" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2239,7 +2240,7 @@
       <c r="S61" s="1"/>
       <c r="T61" s="1"/>
     </row>
-    <row r="62" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N62" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2251,7 +2252,7 @@
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
     </row>
-    <row r="63" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N63" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2263,7 +2264,7 @@
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
     </row>
-    <row r="64" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N64" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2275,7 +2276,7 @@
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
     </row>
-    <row r="65" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N65" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2287,7 +2288,7 @@
       <c r="S65" s="1"/>
       <c r="T65" s="1"/>
     </row>
-    <row r="66" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N66" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2299,7 +2300,7 @@
       <c r="S66" s="1"/>
       <c r="T66" s="1"/>
     </row>
-    <row r="67" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N67" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2311,7 +2312,7 @@
       <c r="S67" s="1"/>
       <c r="T67" s="1"/>
     </row>
-    <row r="68" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N68" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2323,7 +2324,7 @@
       <c r="S68" s="1"/>
       <c r="T68" s="1"/>
     </row>
-    <row r="69" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N69" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2335,7 +2336,7 @@
       <c r="S69" s="1"/>
       <c r="T69" s="1"/>
     </row>
-    <row r="70" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N70" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2347,7 +2348,7 @@
       <c r="S70" s="1"/>
       <c r="T70" s="1"/>
     </row>
-    <row r="71" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N71" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2359,7 +2360,7 @@
       <c r="S71" s="1"/>
       <c r="T71" s="1"/>
     </row>
-    <row r="72" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N72" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2371,7 +2372,7 @@
       <c r="S72" s="1"/>
       <c r="T72" s="1"/>
     </row>
-    <row r="73" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N73" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2383,7 +2384,7 @@
       <c r="S73" s="1"/>
       <c r="T73" s="1"/>
     </row>
-    <row r="74" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N74" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2395,930 +2396,930 @@
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
     </row>
-    <row r="75" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="14:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
